--- a/EKG_Kalite_Yönetim_Sistemi/16_Ürün Tasarımı ve Teknik Doğrulama/03_Tasarım Doğrulama, Test ve Onay/EKG-TAS-FRM-06_tasarim_onayi_ve_seri_uretime_devir_kaydi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/16_Ürün Tasarımı ve Teknik Doğrulama/03_Tasarım Doğrulama, Test ve Onay/EKG-TAS-FRM-06_tasarim_onayi_ve_seri_uretime_devir_kaydi.xlsx
@@ -1295,7 +1295,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-TAS-FRM-06&amp;C&amp;"Arial,Regular"&amp;11Tasarım Onayı ve Seri Üretime Devir Kaydı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 28.09.2026
+Revizyon nedeni: Yanlış standart referansı ve evrensel ürün/seviye varsayımları düzeltildi; devir kararının kapsamı eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
